--- a/data/trans_orig/IP33A-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP33A-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7252</t>
+          <t>7228</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13963</t>
+          <t>13779</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>40,05%</t>
+          <t>39,92%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>77,11%</t>
+          <t>76,1%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8851</t>
+          <t>9359</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16919</t>
+          <t>16811</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>37,53%</t>
+          <t>39,68%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>71,74%</t>
+          <t>71,28%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>18794</t>
+          <t>18421</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>28961</t>
+          <t>28816</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>45,08%</t>
+          <t>44,18%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>69,46%</t>
+          <t>69,12%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4144</t>
+          <t>4328</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10855</t>
+          <t>10879</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>23,9%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>59,95%</t>
+          <t>60,08%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6665</t>
+          <t>6773</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>14733</t>
+          <t>14225</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>28,26%</t>
+          <t>28,72%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>62,47%</t>
+          <t>60,32%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>12731</t>
+          <t>12876</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>22898</t>
+          <t>23271</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>30,54%</t>
+          <t>30,88%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>54,92%</t>
+          <t>55,82%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10189</t>
+          <t>10030</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19634</t>
+          <t>20198</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>25,67%</t>
+          <t>25,27%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>49,47%</t>
+          <t>50,89%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>13400</t>
+          <t>13368</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>23083</t>
+          <t>22970</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>36,37%</t>
+          <t>36,29%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>62,66%</t>
+          <t>62,35%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>26636</t>
+          <t>26147</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>40403</t>
+          <t>41066</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>34,81%</t>
+          <t>34,17%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>52,8%</t>
+          <t>53,66%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>20054</t>
+          <t>19490</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>29499</t>
+          <t>29658</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>50,53%</t>
+          <t>49,11%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>74,33%</t>
+          <t>74,73%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>13756</t>
+          <t>13869</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>23439</t>
+          <t>23471</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>37,34%</t>
+          <t>37,65%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>63,63%</t>
+          <t>63,71%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>36123</t>
+          <t>35460</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>49890</t>
+          <t>50379</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>47,2%</t>
+          <t>46,34%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>65,19%</t>
+          <t>65,83%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>876</t>
+          <t>867</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6623</t>
+          <t>6524</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>28,7%</t>
+          <t>28,27%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1320</t>
+          <t>1349</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6527</t>
+          <t>6333</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>38,75%</t>
+          <t>37,6%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3010</t>
+          <t>3360</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10795</t>
+          <t>10734</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>27,04%</t>
+          <t>26,89%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>16454</t>
+          <t>16553</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>22201</t>
+          <t>22210</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>71,3%</t>
+          <t>71,73%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>10317</t>
+          <t>10511</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>15524</t>
+          <t>15495</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>61,25%</t>
+          <t>62,4%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,16%</t>
+          <t>91,99%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>29126</t>
+          <t>29187</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>36911</t>
+          <t>36561</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>72,96%</t>
+          <t>73,11%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,46%</t>
+          <t>91,58%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>723</t>
+          <t>711</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6218</t>
+          <t>6075</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>33,56%</t>
+          <t>32,79%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2195</t>
+          <t>2169</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8668</t>
+          <t>9216</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>38,85%</t>
+          <t>41,31%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4278</t>
+          <t>4249</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>12901</t>
+          <t>12802</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>31,59%</t>
+          <t>31,35%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>12310</t>
+          <t>12453</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>17805</t>
+          <t>17817</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>66,44%</t>
+          <t>67,21%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>96,16%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>13642</t>
+          <t>13094</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>20115</t>
+          <t>20141</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>61,15%</t>
+          <t>58,69%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,16%</t>
+          <t>90,28%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>27936</t>
+          <t>28035</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>36559</t>
+          <t>36588</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>68,41%</t>
+          <t>68,65%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,52%</t>
+          <t>89,6%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>23078</t>
+          <t>23815</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>38529</t>
+          <t>38629</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>23,22%</t>
+          <t>23,96%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>38,76%</t>
+          <t>38,86%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>31453</t>
+          <t>32140</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>47646</t>
+          <t>48135</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>31,59%</t>
+          <t>32,28%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>47,85%</t>
+          <t>48,34%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>58841</t>
+          <t>59035</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>80769</t>
+          <t>81311</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>29,57%</t>
+          <t>29,67%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>40,59%</t>
+          <t>40,86%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>60871</t>
+          <t>60771</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>76322</t>
+          <t>75585</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>61,24%</t>
+          <t>61,14%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>76,78%</t>
+          <t>76,04%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>51930</t>
+          <t>51441</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>68123</t>
+          <t>67436</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>52,15%</t>
+          <t>51,66%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>68,41%</t>
+          <t>67,72%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>118208</t>
+          <t>117666</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>140136</t>
+          <t>139942</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>59,41%</t>
+          <t>59,14%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>70,43%</t>
+          <t>70,33%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>19029</t>
+          <t>19169</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>27512</t>
+          <t>27501</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>57,01%</t>
+          <t>57,42%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>82,42%</t>
+          <t>82,38%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>17207</t>
+          <t>17471</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>26652</t>
+          <t>26666</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>49,17%</t>
+          <t>49,92%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>76,15%</t>
+          <t>76,19%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>40038</t>
+          <t>39276</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>52064</t>
+          <t>51911</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>58,55%</t>
+          <t>57,44%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>76,14%</t>
+          <t>75,91%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5870</t>
+          <t>5881</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14353</t>
+          <t>14213</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>42,99%</t>
+          <t>42,58%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8346</t>
+          <t>8332</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17791</t>
+          <t>17527</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>23,81%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>50,83%</t>
+          <t>50,08%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>16316</t>
+          <t>16469</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>28342</t>
+          <t>29104</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>24,09%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>41,45%</t>
+          <t>42,56%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16304</t>
+          <t>16453</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>27750</t>
+          <t>27987</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>32,16%</t>
+          <t>32,46%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>54,74%</t>
+          <t>55,21%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9162</t>
+          <t>8689</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19376</t>
+          <t>19510</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>20,78%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>46,33%</t>
+          <t>46,65%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>27502</t>
+          <t>27813</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>43190</t>
+          <t>43957</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>29,73%</t>
+          <t>30,06%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>46,69%</t>
+          <t>47,52%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>22943</t>
+          <t>22706</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>34389</t>
+          <t>34240</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>45,26%</t>
+          <t>44,79%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>67,84%</t>
+          <t>67,54%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>22443</t>
+          <t>22309</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>32657</t>
+          <t>33130</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>53,67%</t>
+          <t>53,35%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>78,09%</t>
+          <t>79,22%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>49321</t>
+          <t>48554</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>65009</t>
+          <t>64698</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>53,31%</t>
+          <t>52,48%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>70,27%</t>
+          <t>69,94%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3410</t>
+          <t>3659</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10801</t>
+          <t>11257</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>41,63%</t>
+          <t>43,38%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1410</t>
+          <t>1909</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7608</t>
+          <t>8260</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>34,7%</t>
+          <t>37,68%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6560</t>
+          <t>6653</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15910</t>
+          <t>16259</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>33,23%</t>
+          <t>33,96%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15148</t>
+          <t>14692</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>22539</t>
+          <t>22290</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>58,37%</t>
+          <t>56,62%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>86,86%</t>
+          <t>85,9%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>14315</t>
+          <t>13663</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>20513</t>
+          <t>20014</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>65,3%</t>
+          <t>62,32%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>91,29%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>31962</t>
+          <t>31613</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>41312</t>
+          <t>41219</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>66,77%</t>
+          <t>66,04%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>86,3%</t>
+          <t>86,1%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3539</t>
+          <t>3444</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10924</t>
+          <t>11100</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>42,16%</t>
+          <t>42,84%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1401</t>
+          <t>1809</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7573</t>
+          <t>7716</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>23,35%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6651</t>
+          <t>6561</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>16675</t>
+          <t>16607</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>28,28%</t>
+          <t>28,16%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>14989</t>
+          <t>14813</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>22374</t>
+          <t>22469</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>57,84%</t>
+          <t>57,16%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,34%</t>
+          <t>86,71%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>25479</t>
+          <t>25336</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>31651</t>
+          <t>31243</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>77,09%</t>
+          <t>76,65%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>94,53%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>42290</t>
+          <t>42358</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>52314</t>
+          <t>52404</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>71,72%</t>
+          <t>71,84%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,72%</t>
+          <t>88,87%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>49611</t>
+          <t>49952</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>69116</t>
+          <t>68870</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>36,5%</t>
+          <t>36,75%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>50,84%</t>
+          <t>50,66%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>35465</t>
+          <t>34716</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>52600</t>
+          <t>52840</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>26,91%</t>
+          <t>26,34%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>39,91%</t>
+          <t>40,09%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>89649</t>
+          <t>90814</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>115651</t>
+          <t>116654</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>33,48%</t>
+          <t>33,92%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>43,2%</t>
+          <t>43,57%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>66820</t>
+          <t>67066</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>86325</t>
+          <t>85984</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>49,16%</t>
+          <t>49,34%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>63,5%</t>
+          <t>63,25%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>79192</t>
+          <t>78952</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>96327</t>
+          <t>97076</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>60,09%</t>
+          <t>59,91%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>73,09%</t>
+          <t>73,66%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>152077</t>
+          <t>151074</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>178079</t>
+          <t>176914</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>56,8%</t>
+          <t>56,43%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>66,52%</t>
+          <t>66,08%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>21777</t>
+          <t>21753</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>31616</t>
+          <t>31291</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>51,85%</t>
+          <t>51,8%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>75,28%</t>
+          <t>74,51%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>22666</t>
+          <t>23253</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>33263</t>
+          <t>33021</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>52,67%</t>
+          <t>54,03%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>77,3%</t>
+          <t>76,73%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>48480</t>
+          <t>47498</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>61805</t>
+          <t>61518</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>57,02%</t>
+          <t>55,86%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>72,69%</t>
+          <t>72,35%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10381</t>
+          <t>10706</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>20220</t>
+          <t>20244</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,72%</t>
+          <t>25,49%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>48,15%</t>
+          <t>48,2%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9770</t>
+          <t>10012</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>20367</t>
+          <t>19780</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>23,27%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>47,33%</t>
+          <t>45,97%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>23224</t>
+          <t>23511</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>36549</t>
+          <t>37531</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>27,31%</t>
+          <t>27,65%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>42,98%</t>
+          <t>44,14%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18437</t>
+          <t>19285</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>29670</t>
+          <t>30028</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>34,91%</t>
+          <t>36,52%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>56,18%</t>
+          <t>56,86%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17522</t>
+          <t>17204</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>29643</t>
+          <t>29729</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>26,52%</t>
+          <t>26,04%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>44,86%</t>
+          <t>44,99%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>40302</t>
+          <t>38606</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>57446</t>
+          <t>56489</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>33,9%</t>
+          <t>32,48%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>48,32%</t>
+          <t>47,52%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>23138</t>
+          <t>22780</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>34371</t>
+          <t>33523</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>43,82%</t>
+          <t>43,14%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>65,09%</t>
+          <t>63,48%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>36429</t>
+          <t>36343</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>48550</t>
+          <t>48868</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>55,14%</t>
+          <t>55,01%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>73,48%</t>
+          <t>73,96%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>61434</t>
+          <t>62391</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>78578</t>
+          <t>80274</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>51,68%</t>
+          <t>52,48%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>66,1%</t>
+          <t>67,52%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9235</t>
+          <t>9121</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>20583</t>
+          <t>20120</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>38,0%</t>
+          <t>37,15%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6817</t>
+          <t>6773</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16189</t>
+          <t>15827</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>35,02%</t>
+          <t>34,24%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>19201</t>
+          <t>18845</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>33996</t>
+          <t>33267</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>19,13%</t>
+          <t>18,77%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>33,87%</t>
+          <t>33,14%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>33576</t>
+          <t>34039</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>44924</t>
+          <t>45038</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>62,0%</t>
+          <t>62,85%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>82,95%</t>
+          <t>83,16%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>30038</t>
+          <t>30400</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>39410</t>
+          <t>39454</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>64,98%</t>
+          <t>65,76%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>85,25%</t>
+          <t>85,35%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>66390</t>
+          <t>67119</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>81185</t>
+          <t>81541</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>66,13%</t>
+          <t>66,86%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>80,87%</t>
+          <t>81,23%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5156</t>
+          <t>5079</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14382</t>
+          <t>13522</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>37,34%</t>
+          <t>35,11%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4789</t>
+          <t>4875</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13793</t>
+          <t>13900</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>37,12%</t>
+          <t>37,4%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>12162</t>
+          <t>12422</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>24633</t>
+          <t>24872</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,55%</t>
+          <t>32,87%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>24134</t>
+          <t>24994</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>33360</t>
+          <t>33437</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>62,66%</t>
+          <t>64,89%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,61%</t>
+          <t>86,81%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>23371</t>
+          <t>23264</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>32375</t>
+          <t>32289</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>62,88%</t>
+          <t>62,6%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,11%</t>
+          <t>86,88%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>51047</t>
+          <t>50808</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>63518</t>
+          <t>63258</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>67,45%</t>
+          <t>67,13%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>83,93%</t>
+          <t>83,59%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>65540</t>
+          <t>65082</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>85500</t>
+          <t>86400</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>34,96%</t>
+          <t>34,71%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>45,6%</t>
+          <t>46,09%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>60337</t>
+          <t>59990</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>82929</t>
+          <t>82457</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>31,34%</t>
+          <t>31,16%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>43,08%</t>
+          <t>42,84%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>132187</t>
+          <t>132385</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>163245</t>
+          <t>161853</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>34,79%</t>
+          <t>34,84%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>42,96%</t>
+          <t>42,6%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>101979</t>
+          <t>101079</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>121939</t>
+          <t>122397</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>54,4%</t>
+          <t>53,91%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>65,04%</t>
+          <t>65,29%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>109567</t>
+          <t>110039</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>132159</t>
+          <t>132506</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>56,92%</t>
+          <t>57,16%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>68,66%</t>
+          <t>68,84%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>216730</t>
+          <t>218122</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>247788</t>
+          <t>247590</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>57,04%</t>
+          <t>57,4%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>65,21%</t>
+          <t>65,16%</t>
         </is>
       </c>
     </row>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4914</t>
+          <t>5055</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10417</t>
+          <t>10505</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>32,8%</t>
+          <t>33,75%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>69,53%</t>
+          <t>70,12%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7547</t>
+          <t>7239</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14035</t>
+          <t>13912</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>38,28%</t>
+          <t>36,72%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>71,2%</t>
+          <t>70,57%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>14135</t>
+          <t>14111</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>23072</t>
+          <t>22434</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>40,74%</t>
+          <t>40,68%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>66,5%</t>
+          <t>64,67%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4564</t>
+          <t>4476</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10067</t>
+          <t>9926</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>30,47%</t>
+          <t>29,88%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>67,2%</t>
+          <t>66,25%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5677</t>
+          <t>5800</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12165</t>
+          <t>12473</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>28,8%</t>
+          <t>29,43%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>61,72%</t>
+          <t>63,28%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>11621</t>
+          <t>12259</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>20558</t>
+          <t>20582</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>33,5%</t>
+          <t>35,33%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>59,26%</t>
+          <t>59,32%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13791</t>
+          <t>13957</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>24502</t>
+          <t>24223</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>37,45%</t>
+          <t>37,9%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>66,54%</t>
+          <t>65,78%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11949</t>
+          <t>12426</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>23548</t>
+          <t>23621</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>27,09%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>51,34%</t>
+          <t>51,5%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>28604</t>
+          <t>28051</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>43738</t>
+          <t>43838</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>34,59%</t>
+          <t>33,92%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>52,89%</t>
+          <t>53,02%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>12324</t>
+          <t>12603</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>23035</t>
+          <t>22869</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>33,46%</t>
+          <t>34,22%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>62,55%</t>
+          <t>62,1%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>22315</t>
+          <t>22242</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>33914</t>
+          <t>33437</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>48,66%</t>
+          <t>48,5%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>73,95%</t>
+          <t>72,91%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>38951</t>
+          <t>38851</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>54085</t>
+          <t>54638</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>47,11%</t>
+          <t>46,98%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>65,41%</t>
+          <t>66,08%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5659</t>
+          <t>6169</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15241</t>
+          <t>15689</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>39,12%</t>
+          <t>40,27%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10298</t>
+          <t>10162</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22558</t>
+          <t>22460</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>20,6%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>45,73%</t>
+          <t>45,54%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>18806</t>
+          <t>19190</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>33968</t>
+          <t>35464</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>21,3%</t>
+          <t>21,74%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>38,48%</t>
+          <t>40,17%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>23717</t>
+          <t>23269</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>33299</t>
+          <t>32789</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>60,88%</t>
+          <t>59,73%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>85,47%</t>
+          <t>84,16%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>26766</t>
+          <t>26864</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>39026</t>
+          <t>39162</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>54,27%</t>
+          <t>54,46%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>79,12%</t>
+          <t>79,4%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>54314</t>
+          <t>52818</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>69476</t>
+          <t>69092</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>61,52%</t>
+          <t>59,83%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>78,7%</t>
+          <t>78,26%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8217</t>
+          <t>8142</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18884</t>
+          <t>19321</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>36,04%</t>
+          <t>36,88%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>18661</t>
+          <t>18938</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>50111</t>
+          <t>48767</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>23,2%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>61,39%</t>
+          <t>59,74%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>31431</t>
+          <t>32090</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>67076</t>
+          <t>67515</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>23,94%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>50,05%</t>
+          <t>50,38%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>33509</t>
+          <t>33072</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>44176</t>
+          <t>44251</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>63,96%</t>
+          <t>63,12%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>84,32%</t>
+          <t>84,46%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>31516</t>
+          <t>32860</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>62966</t>
+          <t>62689</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>38,61%</t>
+          <t>40,26%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>77,14%</t>
+          <t>76,8%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>66944</t>
+          <t>66505</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>102589</t>
+          <t>101930</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>49,95%</t>
+          <t>49,62%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>76,55%</t>
+          <t>76,06%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>40872</t>
+          <t>41113</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>60982</t>
+          <t>60145</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>28,55%</t>
+          <t>28,72%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>42,6%</t>
+          <t>42,01%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>60388</t>
+          <t>60070</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>98421</t>
+          <t>97439</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>30,73%</t>
+          <t>30,57%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>50,08%</t>
+          <t>49,58%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>108098</t>
+          <t>105823</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>150496</t>
+          <t>148957</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>31,82%</t>
+          <t>31,15%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>44,3%</t>
+          <t>43,85%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>82176</t>
+          <t>83013</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>102286</t>
+          <t>102045</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>57,4%</t>
+          <t>57,99%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>71,45%</t>
+          <t>71,28%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>98105</t>
+          <t>99087</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>136138</t>
+          <t>136456</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>49,92%</t>
+          <t>50,42%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>69,27%</t>
+          <t>69,43%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>189188</t>
+          <t>190727</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>231586</t>
+          <t>233861</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>55,7%</t>
+          <t>56,15%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>68,18%</t>
+          <t>68,85%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP33A-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP33A-Edad-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,72 +723,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>12997</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>9222</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>17008</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>55,11%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>39,1%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>72,12%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>10804</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>7228</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>13779</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>7291</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>13936</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>59,67%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>39,92%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>76,1%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>12997</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>9359</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>16811</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>55,11%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>39,68%</t>
+          <t>40,27%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>71,28%</t>
+          <t>76,97%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>18421</t>
+          <t>18209</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>28816</t>
+          <t>28477</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>44,18%</t>
+          <t>43,68%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>69,12%</t>
+          <t>68,3%</t>
         </is>
       </c>
     </row>
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>10587</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>6576</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>14362</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>44,89%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>27,88%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>60,9%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>7303</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>4328</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>10879</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>4171</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>10816</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>40,33%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>23,9%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>60,08%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>10587</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>6773</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>14225</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>44,89%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>28,72%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>60,32%</t>
+          <t>59,73%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>12876</t>
+          <t>13215</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>23271</t>
+          <t>23483</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>30,88%</t>
+          <t>31,7%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>55,82%</t>
+          <t>56,32%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>23584</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>23584</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>23584</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>18107</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>18107</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>18107</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>23584</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>23584</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>23584</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>17853</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>12960</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>22316</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>48,46%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>35,18%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>60,58%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>14857</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>10030</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>20198</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>10197</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>19747</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>37,43%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>25,27%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>50,89%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>17853</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>13368</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>22970</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>48,46%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>36,29%</t>
+          <t>25,69%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>62,35%</t>
+          <t>49,75%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>26147</t>
+          <t>26466</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>41066</t>
+          <t>40985</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>34,17%</t>
+          <t>34,58%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>53,66%</t>
+          <t>53,56%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>18986</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>14523</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>23879</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>51,54%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>39,42%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>64,82%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>24831</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>19490</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>29658</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>19941</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>29491</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>62,57%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>49,11%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>74,73%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>18986</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>13869</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>23471</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>51,54%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>37,65%</t>
+          <t>50,25%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>63,71%</t>
+          <t>74,31%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>35460</t>
+          <t>35541</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>50379</t>
+          <t>50060</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>46,34%</t>
+          <t>46,44%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>65,83%</t>
+          <t>65,42%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>36839</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>36839</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>36839</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>58</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>39688</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>39688</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>39688</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>36839</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>36839</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>36839</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>3519</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1385</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>7023</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>20,89%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>8,22%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>41,69%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>2695</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>867</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>6524</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>657</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>6141</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>11,68%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>3,76%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>28,27%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>3519</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>1349</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>6333</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>20,89%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>37,6%</t>
+          <t>26,61%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3360</t>
+          <t>3226</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10734</t>
+          <t>10752</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>26,89%</t>
+          <t>26,93%</t>
         </is>
       </c>
     </row>
@@ -1522,72 +1522,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>13325</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>9821</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>15459</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>79,11%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>58,31%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>91,78%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>20382</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>16553</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>22210</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>16936</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>22420</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>88,32%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>71,73%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>96,24%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>13325</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>10511</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>15495</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>79,11%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>62,4%</t>
+          <t>73,39%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,99%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>29187</t>
+          <t>29169</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>36561</t>
+          <t>36695</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>73,11%</t>
+          <t>73,07%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,58%</t>
+          <t>91,92%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>16844</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>16844</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>16844</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>34</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>23077</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>23077</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>23077</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>16844</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>16844</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>16844</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>5068</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>2373</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>8889</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>22,71%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>10,64%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>39,84%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>2789</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>711</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>6075</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>744</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>6278</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>15,05%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>3,84%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>32,79%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>5068</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>2169</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>9216</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>22,71%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>41,31%</t>
+          <t>33,89%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4249</t>
+          <t>4200</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>12802</t>
+          <t>12756</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>31,35%</t>
+          <t>31,24%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>17242</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>13421</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>19937</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>77,29%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>60,16%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>89,36%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>15739</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>12453</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>17817</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>12250</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>17784</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>84,95%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>67,21%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>96,16%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>17242</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>13094</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>20141</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>77,29%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>58,69%</t>
+          <t>66,11%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,28%</t>
+          <t>95,99%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>28035</t>
+          <t>28081</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>36588</t>
+          <t>36637</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>68,65%</t>
+          <t>68,76%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,6%</t>
+          <t>89,71%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>22310</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>22310</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>22310</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>18528</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>18528</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>18528</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>22310</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>22310</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>22310</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2095,72 +2095,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>39436</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>31989</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>49008</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>39,6%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>32,12%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>49,22%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>31145</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>23815</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>38629</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>24082</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>38980</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>31,33%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>23,96%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>38,86%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>39436</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>32140</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>48135</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>39,6%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>32,28%</t>
+          <t>24,23%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>48,34%</t>
+          <t>39,22%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>59035</t>
+          <t>59979</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>81311</t>
+          <t>81597</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>29,67%</t>
+          <t>30,14%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>40,86%</t>
+          <t>41,01%</t>
         </is>
       </c>
     </row>
@@ -2208,72 +2208,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>60140</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>50568</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>67587</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>60,4%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>50,78%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>67,88%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>100</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>68255</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>60771</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>75585</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>60420</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>75318</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>68,67%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>61,14%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>76,04%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>60140</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>51441</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>67436</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>60,4%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>51,66%</t>
+          <t>60,78%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>67,72%</t>
+          <t>75,77%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>117666</t>
+          <t>117380</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>139942</t>
+          <t>138998</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>59,14%</t>
+          <t>58,99%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>70,33%</t>
+          <t>69,86%</t>
         </is>
       </c>
     </row>
@@ -2321,57 +2321,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>99576</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>99576</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>99576</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>146</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>99400</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>99400</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>99400</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>148</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>99576</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>99576</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>99576</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2491,7 +2491,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2502,7 +2502,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2670,72 +2670,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>22194</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>17574</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>26742</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>63,42%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>50,21%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>76,41%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>23971</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>19169</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>27501</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>19338</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>27970</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>71,81%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>57,42%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>82,38%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>22194</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>17471</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>26666</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>63,42%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>49,92%</t>
+          <t>57,93%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>76,19%</t>
+          <t>83,79%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>39276</t>
+          <t>38870</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>51911</t>
+          <t>51782</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>57,44%</t>
+          <t>56,84%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>75,91%</t>
+          <t>75,73%</t>
         </is>
       </c>
     </row>
@@ -2783,72 +2783,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>12804</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>8256</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>17424</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>36,58%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>23,59%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>49,79%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>9411</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>5881</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>14213</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>5412</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>14044</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>28,19%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>17,62%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>42,58%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>12804</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>8332</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>17527</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>36,58%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>16,21%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>50,08%</t>
+          <t>42,07%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>16469</t>
+          <t>16598</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>29104</t>
+          <t>29510</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>24,09%</t>
+          <t>24,27%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>42,56%</t>
+          <t>43,16%</t>
         </is>
       </c>
     </row>
@@ -2896,57 +2896,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>34998</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>34998</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>34998</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>51</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>33382</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>33382</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>33382</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>34998</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>34998</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>34998</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3013,72 +3013,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>13890</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>8536</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>19276</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>33,21%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>20,41%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>46,09%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>21827</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>16453</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>27987</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>16346</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>27898</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>43,06%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>32,46%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>55,21%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>13890</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>8689</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>19510</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>33,21%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>32,25%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>46,65%</t>
+          <t>55,03%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>27813</t>
+          <t>27854</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>43957</t>
+          <t>43678</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>30,06%</t>
+          <t>30,11%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>47,52%</t>
+          <t>47,21%</t>
         </is>
       </c>
     </row>
@@ -3126,72 +3126,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>27929</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>22543</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>33283</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>66,79%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>53,91%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>79,59%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>28866</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>22706</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>34240</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>22795</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>34347</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>56,94%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>44,79%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>67,54%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>27929</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>22309</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>33130</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>66,79%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>53,35%</t>
+          <t>44,97%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>79,22%</t>
+          <t>67,75%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>48554</t>
+          <t>48833</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>64698</t>
+          <t>64657</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>52,48%</t>
+          <t>52,79%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>69,94%</t>
+          <t>69,89%</t>
         </is>
       </c>
     </row>
@@ -3239,57 +3239,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>41819</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>41819</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>41819</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>73</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>50693</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>50693</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>50693</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>41819</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>41819</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>41819</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3356,72 +3356,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>4103</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1879</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>7758</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>18,71%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>8,57%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>35,39%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>6646</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>3659</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>11257</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>3525</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>10760</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>25,61%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>14,1%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>43,38%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>4103</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>1909</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>8260</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>18,71%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>37,68%</t>
+          <t>41,46%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6653</t>
+          <t>6283</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>16259</t>
+          <t>15898</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>33,96%</t>
+          <t>33,21%</t>
         </is>
       </c>
     </row>
@@ -3469,72 +3469,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>17820</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>14165</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>20044</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>81,29%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>64,61%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>91,43%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>19303</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>14692</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>22290</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>15189</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>22424</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>74,39%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>56,62%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>85,9%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>17820</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>13663</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>20014</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>81,29%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>62,32%</t>
+          <t>58,54%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,29%</t>
+          <t>86,41%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>31613</t>
+          <t>31974</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>41219</t>
+          <t>41589</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>66,04%</t>
+          <t>66,79%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>86,1%</t>
+          <t>86,88%</t>
         </is>
       </c>
     </row>
@@ -3582,57 +3582,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>21923</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>21923</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>21923</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>25949</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>25949</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>25949</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>21923</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>21923</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>21923</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3699,72 +3699,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>4027</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1429</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>8057</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>12,18%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>4,32%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>24,38%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>6678</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>3444</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>11100</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>3424</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>10805</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>25,77%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>13,29%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>42,84%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>4027</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>1809</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>7716</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>12,18%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>41,7%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6561</t>
+          <t>6389</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>16607</t>
+          <t>16528</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>28,16%</t>
+          <t>28,03%</t>
         </is>
       </c>
     </row>
@@ -3812,72 +3812,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>29025</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>24995</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>31623</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>87,82%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>75,62%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>95,68%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>19235</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>14813</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>22469</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>15108</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>22489</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>74,23%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>57,16%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>86,71%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>29025</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>25336</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>31243</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>87,82%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>76,65%</t>
+          <t>58,3%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,53%</t>
+          <t>86,79%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>42358</t>
+          <t>42437</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>52404</t>
+          <t>52576</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>71,84%</t>
+          <t>71,97%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,87%</t>
+          <t>89,16%</t>
         </is>
       </c>
     </row>
@@ -3925,57 +3925,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>33052</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>33052</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>33052</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>25913</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>25913</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>25913</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>33052</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>33052</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>33052</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>44214</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>35147</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>53885</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>33,55%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>26,67%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>40,89%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>86</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>59122</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>49952</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>68870</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>49748</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>69104</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>43,49%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>36,75%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>50,66%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>44214</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>34716</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>52840</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>33,55%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>26,34%</t>
+          <t>36,6%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>40,09%</t>
+          <t>50,84%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>90814</t>
+          <t>89882</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>116654</t>
+          <t>117033</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>33,92%</t>
+          <t>33,57%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>43,57%</t>
+          <t>43,71%</t>
         </is>
       </c>
     </row>
@@ -4155,72 +4155,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>87578</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>77907</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>96645</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>66,45%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>59,11%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>73,33%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>112</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>76814</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>67066</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>85984</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>66832</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>86188</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>56,51%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>49,34%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>63,25%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>126</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>87578</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>78952</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>97076</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>66,45%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>59,91%</t>
+          <t>49,16%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>73,66%</t>
+          <t>63,4%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>151074</t>
+          <t>150695</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>176914</t>
+          <t>177846</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>56,43%</t>
+          <t>56,29%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>66,08%</t>
+          <t>66,43%</t>
         </is>
       </c>
     </row>
@@ -4268,57 +4268,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>187</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>131792</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>131792</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>131792</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>198</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>135936</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>135936</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>135936</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>187</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>131792</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>131792</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>131792</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4438,7 +4438,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4449,7 +4449,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4617,72 +4617,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>28247</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>22426</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>33068</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>65,64%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>52,11%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>76,84%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>27111</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>21753</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>31291</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>22141</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>31605</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>64,55%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>51,8%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>74,51%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>28247</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>23253</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>33021</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>65,64%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>54,03%</t>
+          <t>52,72%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>76,73%</t>
+          <t>75,25%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>47498</t>
+          <t>48444</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>61518</t>
+          <t>62155</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>55,86%</t>
+          <t>56,97%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>72,35%</t>
+          <t>73,1%</t>
         </is>
       </c>
     </row>
@@ -4730,72 +4730,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>14786</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>9965</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>20607</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>34,36%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>23,16%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>47,89%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>14886</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>10706</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>20244</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>10392</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>19856</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>35,45%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>25,49%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>48,2%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>14786</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>10012</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>19780</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>34,36%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>24,75%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>45,97%</t>
+          <t>47,28%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>23511</t>
+          <t>22874</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>37531</t>
+          <t>36585</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>27,65%</t>
+          <t>26,9%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>44,14%</t>
+          <t>43,03%</t>
         </is>
       </c>
     </row>
@@ -4843,57 +4843,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>43033</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>43033</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>43033</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>68</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>41997</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>41997</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>41997</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>43033</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>43033</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>43033</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4960,72 +4960,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>23046</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>17588</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>29525</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>34,88%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>26,62%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>44,69%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>38</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>24637</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>19285</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>30028</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>19070</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>30437</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>46,65%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>36,52%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>56,86%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>23046</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>17204</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>29729</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>34,88%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>26,04%</t>
+          <t>36,11%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>44,99%</t>
+          <t>57,64%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>38606</t>
+          <t>38876</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>56489</t>
+          <t>56102</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>32,48%</t>
+          <t>32,7%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>47,52%</t>
+          <t>47,19%</t>
         </is>
       </c>
     </row>
@@ -5073,72 +5073,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>43026</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>36547</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>48484</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>65,12%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>55,31%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>73,38%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>28171</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>22780</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>33523</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>22371</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>33738</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>53,35%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>43,14%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>63,48%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>43026</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>36343</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>48868</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>65,12%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>55,01%</t>
+          <t>42,36%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>73,96%</t>
+          <t>63,89%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>62391</t>
+          <t>62778</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>80274</t>
+          <t>80004</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>52,48%</t>
+          <t>52,81%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>67,52%</t>
+          <t>67,3%</t>
         </is>
       </c>
     </row>
@@ -5186,57 +5186,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>66072</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>66072</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>66072</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>82</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>52808</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>52808</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>52808</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>66072</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>66072</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>66072</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5303,72 +5303,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>11044</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>6634</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>16473</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>23,89%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>14,35%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>35,63%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>14551</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>9121</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>20120</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>9805</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>20443</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>26,87%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>16,84%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>37,15%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>11044</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>6773</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>15827</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>23,89%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>34,24%</t>
+          <t>37,75%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>18845</t>
+          <t>19264</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>33267</t>
+          <t>33380</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>19,19%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>33,14%</t>
+          <t>33,25%</t>
         </is>
       </c>
     </row>
@@ -5416,72 +5416,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>35183</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>29754</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>39593</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>76,11%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>64,37%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>85,65%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>55</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>39608</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>34039</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>45038</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>33716</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>44354</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>73,13%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>62,85%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>83,16%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>35183</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>30400</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>39454</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>76,11%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>65,76%</t>
+          <t>62,25%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>85,35%</t>
+          <t>81,9%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>67119</t>
+          <t>67006</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>81541</t>
+          <t>81122</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>66,86%</t>
+          <t>66,75%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>81,23%</t>
+          <t>80,81%</t>
         </is>
       </c>
     </row>
@@ -5529,57 +5529,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>46227</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>46227</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>46227</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>76</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>54159</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>54159</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>54159</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>46227</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>46227</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>46227</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5646,72 +5646,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>8755</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>4817</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>13705</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>23,56%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>12,96%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>36,88%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>9086</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>5079</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>13522</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>5138</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>14126</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>23,59%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>13,19%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>35,11%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>8755</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>4875</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>13900</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>23,56%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>37,4%</t>
+          <t>36,68%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>12422</t>
+          <t>12186</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>24872</t>
+          <t>24865</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,1%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,87%</t>
+          <t>32,86%</t>
         </is>
       </c>
     </row>
@@ -5759,72 +5759,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>28409</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>23459</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>32347</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>76,44%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>63,12%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>87,04%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>29430</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>24994</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>33437</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>24390</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>33378</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>76,41%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>64,89%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>86,81%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>28409</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>23264</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>32289</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>76,44%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>62,6%</t>
+          <t>63,32%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,88%</t>
+          <t>86,66%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>50808</t>
+          <t>50815</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>63258</t>
+          <t>63494</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>67,13%</t>
+          <t>67,14%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>83,59%</t>
+          <t>83,9%</t>
         </is>
       </c>
     </row>
@@ -5872,57 +5872,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>37164</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>37164</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>37164</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>56</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>38516</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>38516</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>38516</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>37164</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>37164</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>37164</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5989,107 +5989,107 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>71091</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>61208</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>82567</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>36,93%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>31,8%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>42,89%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>117</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>75384</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>65082</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>86400</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>64356</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>85615</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>40,21%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>34,71%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>46,09%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>103</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>71091</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>59990</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>82457</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>36,93%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>31,16%</t>
+          <t>34,33%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
+          <t>45,67%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>146475</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>130916</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>162798</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>38,55%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>34,45%</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
           <t>42,84%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>220</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>146475</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>132385</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>161853</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>38,55%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>34,84%</t>
-        </is>
-      </c>
-      <c r="W16" s="2" t="inlineStr">
-        <is>
-          <t>42,6%</t>
         </is>
       </c>
     </row>
@@ -6102,107 +6102,107 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>121405</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>109929</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>131288</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>63,07%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>57,11%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>68,2%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>165</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>112095</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>101079</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>122397</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>101864</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>123123</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>59,79%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>53,91%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>65,29%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>171</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>121405</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>110039</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>132506</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>63,07%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
+          <t>54,33%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>65,67%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>233500</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>217177</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>249059</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>61,45%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
           <t>57,16%</t>
         </is>
       </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>68,84%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>336</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>233500</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>218122</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>247590</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>61,45%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>57,4%</t>
-        </is>
-      </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>65,16%</t>
+          <t>65,55%</t>
         </is>
       </c>
     </row>
@@ -6215,57 +6215,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>274</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>192496</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>192496</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>192496</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>282</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>187479</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>187479</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>187479</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>274</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>192496</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>192496</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>192496</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6385,7 +6385,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6396,7 +6396,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6564,72 +6564,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>8593</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>5751</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>11449</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>51,58%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>34,52%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>68,72%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>7737</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>5055</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>10505</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>51,65%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>33,75%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>70,12%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>10703</t>
+          <t>6982</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7239</t>
+          <t>4286</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13912</t>
+          <t>9497</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>54,3%</t>
+          <t>51,35%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>36,72%</t>
+          <t>31,52%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>70,57%</t>
+          <t>69,83%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>18441</t>
+          <t>15576</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>14111</t>
+          <t>11624</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>22434</t>
+          <t>19335</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>53,15%</t>
+          <t>51,48%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>40,68%</t>
+          <t>38,42%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>64,67%</t>
+          <t>63,9%</t>
         </is>
       </c>
     </row>
@@ -6677,72 +6677,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>8066</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>5210</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>10908</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>48,42%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>31,28%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>65,48%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>7244</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>4476</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>9926</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>48,35%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>29,88%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>66,25%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>9009</t>
+          <t>6617</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5800</t>
+          <t>4102</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12473</t>
+          <t>9313</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>45,7%</t>
+          <t>48,65%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>29,43%</t>
+          <t>30,17%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>63,28%</t>
+          <t>68,48%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>16252</t>
+          <t>14682</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>12259</t>
+          <t>10923</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>20582</t>
+          <t>18634</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>46,85%</t>
+          <t>48,52%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>35,33%</t>
+          <t>36,1%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>59,32%</t>
+          <t>61,58%</t>
         </is>
       </c>
     </row>
@@ -6790,57 +6790,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>16659</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>16659</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>16659</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>14981</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>14981</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>14981</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>19712</t>
+          <t>13599</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>19712</t>
+          <t>13599</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>19712</t>
+          <t>13599</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>34693</t>
+          <t>30258</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>34693</t>
+          <t>30258</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>34693</t>
+          <t>30258</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6907,72 +6907,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>14741</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>10204</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>19209</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>38,65%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>26,75%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>50,36%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>18570</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>13957</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>24223</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>50,43%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>37,9%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>65,78%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>17583</t>
+          <t>14999</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12426</t>
+          <t>10906</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>23621</t>
+          <t>19666</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>38,34%</t>
+          <t>47,28%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>27,09%</t>
+          <t>34,38%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>51,5%</t>
+          <t>61,99%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>36153</t>
+          <t>29740</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>28051</t>
+          <t>23376</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>43838</t>
+          <t>36209</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>43,72%</t>
+          <t>42,57%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>33,92%</t>
+          <t>33,46%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>53,02%</t>
+          <t>51,83%</t>
         </is>
       </c>
     </row>
@@ -7020,72 +7020,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>23402</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>18934</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>27939</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>61,35%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>49,64%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>73,25%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>18256</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>12603</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>22869</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>49,57%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>34,22%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>62,1%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>28280</t>
+          <t>16726</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>22242</t>
+          <t>12059</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>33437</t>
+          <t>20819</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>61,66%</t>
+          <t>52,72%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>48,5%</t>
+          <t>38,01%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>72,91%</t>
+          <t>65,62%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>46536</t>
+          <t>40128</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>38851</t>
+          <t>33659</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>54638</t>
+          <t>46492</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>56,28%</t>
+          <t>57,43%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>46,98%</t>
+          <t>48,17%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>66,08%</t>
+          <t>66,54%</t>
         </is>
       </c>
     </row>
@@ -7133,57 +7133,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>38143</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>38143</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>38143</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>58</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>36826</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>36826</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>36826</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>45863</t>
+          <t>31725</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>45863</t>
+          <t>31725</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>45863</t>
+          <t>31725</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>82689</t>
+          <t>69868</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>82689</t>
+          <t>69868</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>82689</t>
+          <t>69868</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7250,72 +7250,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>14784</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>9737</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>20380</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>31,83%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>20,96%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>43,88%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>10535</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>6169</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>15689</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>27,04%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>15,84%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>40,27%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>15584</t>
+          <t>10996</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10162</t>
+          <t>7008</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22460</t>
+          <t>16609</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>31,6%</t>
+          <t>29,25%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>18,64%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>45,54%</t>
+          <t>44,18%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>26119</t>
+          <t>25780</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>19190</t>
+          <t>18433</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>35464</t>
+          <t>33300</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>29,59%</t>
+          <t>30,68%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>21,93%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>40,17%</t>
+          <t>39,62%</t>
         </is>
       </c>
     </row>
@@ -7368,32 +7368,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>28423</t>
+          <t>31665</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>23269</t>
+          <t>26069</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>32789</t>
+          <t>36712</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>72,96%</t>
+          <t>68,17%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>59,73%</t>
+          <t>56,12%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>84,16%</t>
+          <t>79,04%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7403,32 +7403,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>33740</t>
+          <t>26597</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>26864</t>
+          <t>20984</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>39162</t>
+          <t>30585</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>68,4%</t>
+          <t>70,75%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>54,46%</t>
+          <t>55,82%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>79,4%</t>
+          <t>81,36%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>62163</t>
+          <t>58262</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>52818</t>
+          <t>50742</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>69092</t>
+          <t>65609</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>70,41%</t>
+          <t>69,32%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>59,83%</t>
+          <t>60,38%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>78,26%</t>
+          <t>78,07%</t>
         </is>
       </c>
     </row>
@@ -7476,57 +7476,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>46449</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>46449</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>46449</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>51</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>38958</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>38958</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>38958</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>49324</t>
+          <t>37593</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>49324</t>
+          <t>37593</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>49324</t>
+          <t>37593</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>88282</t>
+          <t>84042</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>88282</t>
+          <t>84042</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>88282</t>
+          <t>84042</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7593,72 +7593,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>28563</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>17674</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>46234</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>38,24%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>23,66%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>61,9%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>13199</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>8142</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>19321</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>25,19%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>15,54%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>36,88%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>31631</t>
+          <t>13455</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>18938</t>
+          <t>8691</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>48767</t>
+          <t>19967</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>38,75%</t>
+          <t>24,09%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>59,74%</t>
+          <t>35,75%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>44830</t>
+          <t>42018</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>32090</t>
+          <t>30367</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>67515</t>
+          <t>62079</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>33,45%</t>
+          <t>32,19%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>23,94%</t>
+          <t>23,26%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>50,38%</t>
+          <t>47,56%</t>
         </is>
       </c>
     </row>
@@ -7711,32 +7711,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>39194</t>
+          <t>46127</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>33072</t>
+          <t>28456</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>44251</t>
+          <t>57016</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>74,81%</t>
+          <t>61,76%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>63,12%</t>
+          <t>38,1%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>84,46%</t>
+          <t>76,34%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7746,32 +7746,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>49996</t>
+          <t>42391</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>32860</t>
+          <t>35879</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>62689</t>
+          <t>47155</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>61,25%</t>
+          <t>75,91%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>40,26%</t>
+          <t>64,25%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>76,8%</t>
+          <t>84,44%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>89190</t>
+          <t>88519</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>66505</t>
+          <t>68458</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>101930</t>
+          <t>100170</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>66,55%</t>
+          <t>67,81%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>49,62%</t>
+          <t>52,44%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>76,06%</t>
+          <t>76,74%</t>
         </is>
       </c>
     </row>
@@ -7819,57 +7819,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>74690</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>74690</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>74690</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>74</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>52393</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>52393</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>52393</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>81627</t>
+          <t>55846</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>81627</t>
+          <t>55846</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>81627</t>
+          <t>55846</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>134020</t>
+          <t>130537</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>134020</t>
+          <t>130537</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>134020</t>
+          <t>130537</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7936,72 +7936,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>66682</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>54366</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>84014</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>37,9%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>30,9%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>47,75%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>78</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>50041</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>41113</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>60145</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>34,95%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>28,72%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>42,01%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>75501</t>
+          <t>46432</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>60070</t>
+          <t>37189</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>97439</t>
+          <t>55901</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>38,42%</t>
+          <t>33,46%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>26,8%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>49,58%</t>
+          <t>40,29%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>125542</t>
+          <t>113114</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>105823</t>
+          <t>98842</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>148957</t>
+          <t>135046</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>36,96%</t>
+          <t>35,94%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>31,15%</t>
+          <t>31,41%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>43,85%</t>
+          <t>42,91%</t>
         </is>
       </c>
     </row>
@@ -8049,72 +8049,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>109260</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>91928</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>121576</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>62,1%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>52,25%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>69,1%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>135</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>93117</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>83013</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>102045</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>65,05%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>57,99%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>71,28%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>147</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>121025</t>
+          <t>92331</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>99087</t>
+          <t>82862</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>136456</t>
+          <t>101574</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>61,58%</t>
+          <t>66,54%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>50,42%</t>
+          <t>59,71%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>69,43%</t>
+          <t>73,2%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>214142</t>
+          <t>201591</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>190727</t>
+          <t>179659</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>233861</t>
+          <t>215863</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>63,04%</t>
+          <t>64,06%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>56,15%</t>
+          <t>57,09%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>68,85%</t>
+          <t>68,59%</t>
         </is>
       </c>
     </row>
@@ -8162,57 +8162,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>175942</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>175942</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>175942</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>213</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>143158</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>143158</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>143158</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>240</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>196526</t>
+          <t>138763</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>196526</t>
+          <t>138763</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>196526</t>
+          <t>138763</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>339684</t>
+          <t>314705</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>339684</t>
+          <t>314705</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>339684</t>
+          <t>314705</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
